--- a/week 01/Ex4C_GTrends_marketing.xlsx
+++ b/week 01/Ex4C_GTrends_marketing.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alondramartinez\Documents\DataAnalytics\week 01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{83A8C58E-AF8E-44BA-9E0A-7276F1AF6C0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1CD431ED-B0A4-472E-862E-BF52A3CF5DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{F9DB008F-A326-42B6-8C36-8BB36543A99E}"/>
   </bookViews>
   <sheets>
     <sheet name="by search term" sheetId="1" r:id="rId1"/>
     <sheet name="by state" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="4" state="hidden" r:id="rId3"/>
     <sheet name="sales region lookup" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
@@ -23,7 +23,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="16" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -745,7 +745,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="19"/>
@@ -755,7 +755,6 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="11"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="42" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2081,7 +2080,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{01F04F2C-8BDA-4A2B-8CBC-FC6278EF0979}" name="PivotTable5" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{01F04F2C-8BDA-4A2B-8CBC-FC6278EF0979}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A15:C26" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" showAll="0">
@@ -4288,123 +4287,123 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>60</v>
       </c>
       <c r="B16" s="1">
         <v>0.67</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16">
         <v>0.2</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="7" t="s">
         <v>61</v>
       </c>
       <c r="B17" s="1">
         <v>0.75</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17">
         <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="7" t="s">
         <v>59</v>
       </c>
       <c r="B18" s="1">
         <v>0.68</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18">
         <v>0.18</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
         <v>32</v>
       </c>
       <c r="B19" s="1">
         <v>0.48</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19">
         <v>0.12</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="7" t="s">
         <v>51</v>
       </c>
       <c r="B20" s="1">
         <v>0.54</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20">
         <v>0.08</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="7" t="s">
         <v>46</v>
       </c>
       <c r="B21" s="1">
         <v>0.59</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21">
         <v>0.08</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="7" t="s">
         <v>53</v>
       </c>
       <c r="B22" s="1">
         <v>0.61</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="7" t="s">
         <v>54</v>
       </c>
       <c r="B23" s="1">
         <v>0.67</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23">
         <v>0.06</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="7" t="s">
         <v>22</v>
       </c>
       <c r="B24" s="1">
         <v>0.42</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24">
         <v>0.15</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="7" t="s">
         <v>52</v>
       </c>
       <c r="B25" s="1">
         <v>0.54</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25">
         <v>0.08</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="7" t="s">
         <v>72</v>
       </c>
       <c r="B26" s="1">
         <v>5.95</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26">
         <v>1.1599999999999999</v>
       </c>
     </row>
